--- a/Client/Configs/GameConfig/Datas/skill.xlsx
+++ b/Client/Configs/GameConfig/Datas/skill.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,43 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <color rgb="007F6000"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,20 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,76 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>技能主表：一个技能一行。原型阶段优先改这里。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>技能ID。必须唯一；同步、存档、日志都用这个稳定ID。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>程序用Key。建议英文小写，下划线分隔；不要随意改已上线Key。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>技能显示名。UI和调试日志给人看的名字。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>技能描述。策划备注/UI描述都可以先写这里。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>目标类型。当前支持 EnemySingle：敌方单体。后续可扩展 Self/Ally/AOE。</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>效果ID。指向 effect.xlsx，决定伤害、治疗、控制、加Buff等逻辑效果。</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>投射物ID。指向 projectile.xlsx，决定飞行速度、特效Prefab、命中特效。</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>冷却时间，单位秒。AI自动战斗会按这个判断能不能释放。</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>施法距离，单位米。目标超出范围时会先靠近。</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>动画Key。当前原型用 Attack1，后续通过配置映射到具体动画片段。</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>同步事件Key。联机时用于表达这次释放技能是什么事件。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -525,362 +413,344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>skillKey</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>targetType</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>effectId</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>projectileId</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>cooldown</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>range</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>defaultLevel</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>animationKey</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>syncEventKey</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>技能ID。必须唯一；同步、存档、日志都用这个稳定ID。</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>程序用Key。建议英文小写，下划线分隔；不要随意改已上线Key。</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>技能显示名。UI和调试日志给人看的名字。</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>技能描述。策划备注/UI描述都可以先写这里。</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>目标类型。当前支持 EnemySingle：敌方单体。后续可扩展 Self/Ally/AOE。</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>效果ID。指向 effect.xlsx，决定伤害、治疗、控制、加Buff等逻辑效果。</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>投射物ID。指向 projectile.xlsx，决定飞行速度、特效Prefab、命中特效。</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>冷却时间，单位秒。AI自动战斗会按这个判断能不能释放。</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>施法距离，单位米。目标超出范围时会先靠近。</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>动画Key。当前原型用 Attack1，后续通过配置映射到具体动画片段。</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>同步事件Key。联机时用于表达这次释放技能是什么事件。</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Stable skill id.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Program key.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Display name.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Description.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Target type.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Default level.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Animation key.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sync event key.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n">
-        <v>100101</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>frostbolt</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>寒冰箭</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>发射寒冰箭攻击单个敌人，造成固定冰霜伤害。后续可追加减速Buff。</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Frostbolt</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Damage and slow one enemy.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>200101</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>300101</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Attack1</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>combat.cast_skill</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n">
-        <v>100102</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>fireball</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>火球术</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>发射火球攻击单个敌人，造成固定火焰伤害。后续可追加灼烧Buff。</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fireball</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Damage and burn one enemy.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>EnemySingle</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>200102</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>300102</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Attack1</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Heal one ally.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AllySingle</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>devotion_aura</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Devotion Aura</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aura that grants armor to nearby allies.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>combat.cast_skill</t>
         </is>
@@ -888,6 +758,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Client/Configs/GameConfig/Datas/skill.xlsx
+++ b/Client/Configs/GameConfig/Datas/skill.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,26 @@
           <t>syncEventKey</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>resourceType</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>castMode</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>targetRule</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>threatMultiplier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +529,26 @@
           <t>string</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +596,26 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,24 +663,44 @@
           <t>Sync event key.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Resource type.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cast mode.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Target rule.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Threat multiplier.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>frostbolt</t>
+          <t>warrior_basic_attack</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Frostbolt</t>
+          <t>Warrior Strike</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Damage and slow one enemy.</t>
+          <t>Melee basic attack. Generates rage.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -640,25 +720,43 @@
         <is>
           <t>combat.cast_skill</t>
         </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rage</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Melee</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fireball</t>
+          <t>warrior_charge</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fireball</t>
+          <t>Charge</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Damage and burn one enemy.</t>
+          <t>Rush to target and stun non-boss enemy.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -671,37 +769,55 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Attack1</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>combat.cast_skill</t>
         </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Rage</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>1003</v>
+        <v>1103</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>heal</t>
+          <t>thunder_clap</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>Thunder Clap</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Heal one ally.</t>
+          <t>Area damage, high threat, attack-speed slow.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AllySingle</t>
+          <t>EnemyArea</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -716,44 +832,416 @@
         <is>
           <t>combat.cast_skill</t>
         </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Rage</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AreaEnemy</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
+        <v>1201</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mage_basic_shot</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Arcane Shot</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ranged basic attack.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EnemySingle</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>frostbolt</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Frostbolt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Damage and slow one enemy.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>EnemySingle</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fireball</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fireball</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Damage and burn one enemy.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EnemySingle</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1301</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>priest_basic_shot</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Holy Bolt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ranged basic attack.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EnemySingle</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1302</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Heal lowest HP ally.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AllySingle</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AllyLowestHp</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1303</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>resurrection</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Resurrection</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Revive a defeated ally.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DeadAlly</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Attack1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>combat.cast_skill</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Mana</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>DeadAlly</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
         <v>1004</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>devotion_aura</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Devotion Aura</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Aura that grants armor to nearby allies.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Aura</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Attack1</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>combat.cast_skill</t>
         </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
